--- a/Assets/Json loader/excel_files/PlayerTowerStatDatas.xlsx
+++ b/Assets/Json loader/excel_files/PlayerTowerStatDatas.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>key</t>
   </si>
@@ -45,13 +45,40 @@
   </si>
   <si>
     <t>기본 체력</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>200\</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="64" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+    <numFmt numFmtId="65" formatCode="@"/>
+  </numFmts>
   <fonts count="20">
     <font>
       <sz val="11.0"/>
@@ -401,7 +428,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -410,7 +436,6 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -419,7 +444,6 @@
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -428,7 +452,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -443,7 +466,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -458,7 +480,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -473,7 +494,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -482,7 +502,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -493,7 +512,6 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
@@ -645,8 +663,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="64" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="65" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="65" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="65" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="65" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
@@ -965,9 +992,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
+    <col min="1" max="1" width="9.88000011" customWidth="1" outlineLevel="0"/>
     <col min="2" max="2" width="13.13000011" customWidth="1" outlineLevel="0"/>
     <col min="3" max="3" width="17.12999916" customWidth="1" outlineLevel="0"/>
     <col min="4" max="4" width="12.88000011" customWidth="1" outlineLevel="0"/>
@@ -1022,11 +1050,11 @@
         <v>2</v>
       </c>
       <c r="B5" s="0">
-        <f>$B$4+($A5-1)*20</f>
-        <v>120</v>
+        <f>$B$4+($A5-1)*50</f>
+        <v>150</v>
       </c>
       <c r="C5" s="0">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1034,12 +1062,30 @@
         <v>3</v>
       </c>
       <c r="B6" s="0">
-        <f>$B$4+($A6-1)*20</f>
-        <v>140</v>
+        <f>$B$4+($A6-1)*50</f>
+        <v>200</v>
       </c>
       <c r="C6" s="0">
-        <v>14</v>
-      </c>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
